--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Airline_Cumulative_Statistics_2019.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Airline_Cumulative_Statistics_2019.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Delta</t>
@@ -163,7 +166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -186,40 +189,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
@@ -309,37 +312,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>210838822730</v>
+        <v>212837239427</v>
       </c>
       <c r="C4" s="0">
-        <v>246409171517</v>
+        <v>248814510137</v>
       </c>
       <c r="D4" s="0">
-        <v>812910</v>
+        <v>804028</v>
       </c>
       <c r="E4" s="0">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F4" s="0">
-        <v>1086789</v>
+        <v>1115245</v>
       </c>
       <c r="G4" s="0">
-        <v>3.5899999999999999</v>
+        <v>3.6000000000000001</v>
       </c>
       <c r="H4" s="0">
-        <v>11.19</v>
+        <v>11.140000000000001</v>
       </c>
       <c r="I4" s="0">
-        <v>85.560000000000002</v>
+        <v>85.540000000000006</v>
       </c>
       <c r="J4" s="0">
-        <v>1218</v>
+        <v>1202</v>
       </c>
       <c r="K4" s="0">
-        <v>5605.1499999999996</v>
+        <v>5582.2799999999997</v>
       </c>
       <c r="L4" s="0">
-        <v>31.039999999999999</v>
+        <v>31.02</v>
       </c>
       <c r="M4" s="0">
         <v>0.076999999999999999</v>
@@ -350,40 +353,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>205070083536</v>
+        <v>8827043</v>
       </c>
       <c r="C5" s="0">
-        <v>235945861860</v>
+        <v>16154100</v>
       </c>
       <c r="D5" s="0">
-        <v>825967</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F5" s="0">
-        <v>960597</v>
+        <v>198</v>
       </c>
       <c r="G5" s="0">
-        <v>3.3599999999999999</v>
+        <v>0</v>
       </c>
       <c r="H5" s="0">
-        <v>10.68</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>86.909999999999997</v>
+        <v>54.640000000000001</v>
       </c>
       <c r="J5" s="0">
-        <v>1277</v>
+        <v>544</v>
       </c>
       <c r="K5" s="0">
-        <v>4838.4499999999998</v>
+        <v>0</v>
       </c>
       <c r="L5" s="0">
-        <v>25.98</v>
+        <v>0</v>
       </c>
       <c r="M5" s="0">
-        <v>0.063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -391,40 +394,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>24191529199</v>
+        <v>217178640851</v>
       </c>
       <c r="C6" s="0">
-        <v>28103915678</v>
+        <v>250098611505</v>
       </c>
       <c r="D6" s="0">
-        <v>833697</v>
+        <v>774851</v>
       </c>
       <c r="E6" s="0">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="F6" s="0">
-        <v>138561</v>
+        <v>1147622</v>
       </c>
       <c r="G6" s="0">
-        <v>4.1100000000000003</v>
+        <v>3.5600000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>11.550000000000001</v>
+        <v>10.390000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>86.079999999999998</v>
+        <v>86.840000000000003</v>
       </c>
       <c r="J6" s="0">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="K6" s="0">
-        <v>3895.5700000000002</v>
+        <v>4782.1300000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>20.190000000000001</v>
+        <v>26.109999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.053999999999999999</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -432,40 +435,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>17809813684</v>
+        <v>24191529199</v>
       </c>
       <c r="C7" s="0">
-        <v>20564411683</v>
+        <v>28103915678</v>
       </c>
       <c r="D7" s="0">
-        <v>976932</v>
+        <v>833697</v>
       </c>
       <c r="E7" s="0">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="F7" s="0">
-        <v>89355</v>
+        <v>138561</v>
       </c>
       <c r="G7" s="0">
-        <v>4.2400000000000002</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="H7" s="0">
-        <v>10.16</v>
+        <v>11.550000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>86.609999999999999</v>
+        <v>86.079999999999998</v>
       </c>
       <c r="J7" s="0">
-        <v>961</v>
+        <v>1050</v>
       </c>
       <c r="K7" s="0">
-        <v>6180.8500000000004</v>
+        <v>3895.5700000000002</v>
       </c>
       <c r="L7" s="0">
-        <v>27.550000000000001</v>
+        <v>20.190000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.053999999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -473,40 +476,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>53617847335</v>
+        <v>17809813684</v>
       </c>
       <c r="C8" s="0">
-        <v>63829153132</v>
+        <v>20564411683</v>
       </c>
       <c r="D8" s="0">
-        <v>689523</v>
+        <v>976932</v>
       </c>
       <c r="E8" s="0">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="F8" s="0">
-        <v>369234</v>
+        <v>89355</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9900000000000002</v>
+        <v>4.2400000000000002</v>
       </c>
       <c r="H8" s="0">
-        <v>11.85</v>
+        <v>10.16</v>
       </c>
       <c r="I8" s="0">
-        <v>84</v>
+        <v>86.609999999999999</v>
       </c>
       <c r="J8" s="0">
-        <v>1137</v>
+        <v>961</v>
       </c>
       <c r="K8" s="0">
-        <v>3909.5500000000002</v>
+        <v>6180.8500000000004</v>
       </c>
       <c r="L8" s="0">
-        <v>26.16</v>
+        <v>27.550000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.067000000000000004</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -514,40 +517,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>131375009633</v>
+        <v>53617847335</v>
       </c>
       <c r="C9" s="0">
-        <v>157288255663</v>
+        <v>63829153132</v>
       </c>
       <c r="D9" s="0">
-        <v>573354</v>
+        <v>689523</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="F9" s="0">
-        <v>1367938</v>
+        <v>369234</v>
       </c>
       <c r="G9" s="0">
-        <v>4.9900000000000002</v>
+        <v>3.9900000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>10.140000000000001</v>
+        <v>11.85</v>
       </c>
       <c r="I9" s="0">
-        <v>83.519999999999996</v>
+        <v>84</v>
       </c>
       <c r="J9" s="0">
-        <v>748</v>
+        <v>1137</v>
       </c>
       <c r="K9" s="0">
-        <v>3845.71</v>
+        <v>3909.5500000000002</v>
       </c>
       <c r="L9" s="0">
-        <v>25.149999999999999</v>
+        <v>26.16</v>
       </c>
       <c r="M9" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="10">
@@ -555,40 +558,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>35245109332</v>
+        <v>131375009633</v>
       </c>
       <c r="C10" s="0">
-        <v>41817093806</v>
+        <v>157288255663</v>
       </c>
       <c r="D10" s="0">
-        <v>850460</v>
+        <v>573354</v>
       </c>
       <c r="E10" s="0">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="F10" s="0">
-        <v>225262</v>
+        <v>1367938</v>
       </c>
       <c r="G10" s="0">
-        <v>4.5800000000000001</v>
+        <v>4.9900000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>12.24</v>
+        <v>10.140000000000001</v>
       </c>
       <c r="I10" s="0">
-        <v>84.280000000000001</v>
+        <v>83.519999999999996</v>
       </c>
       <c r="J10" s="0">
-        <v>1009</v>
+        <v>748</v>
       </c>
       <c r="K10" s="0">
-        <v>3474.73</v>
+        <v>3845.71</v>
       </c>
       <c r="L10" s="0">
-        <v>18.879999999999999</v>
+        <v>25.149999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="11">
@@ -596,40 +599,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>5267390979</v>
+        <v>35245109332</v>
       </c>
       <c r="C11" s="0">
-        <v>6638788455</v>
+        <v>41817093806</v>
       </c>
       <c r="D11" s="0">
-        <v>610744</v>
+        <v>850460</v>
       </c>
       <c r="E11" s="0">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F11" s="0">
-        <v>30320</v>
+        <v>225262</v>
       </c>
       <c r="G11" s="0">
-        <v>2.79</v>
+        <v>4.5800000000000001</v>
       </c>
       <c r="H11" s="0">
-        <v>8.6699999999999999</v>
+        <v>12.24</v>
       </c>
       <c r="I11" s="0">
-        <v>79.340000000000003</v>
+        <v>84.280000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>1223</v>
+        <v>1009</v>
       </c>
       <c r="K11" s="0">
-        <v>3765.3699999999999</v>
+        <v>3474.73</v>
       </c>
       <c r="L11" s="0">
-        <v>21.050000000000001</v>
+        <v>18.879999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.052999999999999999</v>
+        <v>0.050000000000000003</v>
       </c>
     </row>
     <row r="12">
@@ -637,40 +640,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>213040596842</v>
+        <v>5267390979</v>
       </c>
       <c r="C12" s="0">
-        <v>252985679341</v>
+        <v>6638788455</v>
       </c>
       <c r="D12" s="0">
-        <v>0</v>
+        <v>610744</v>
       </c>
       <c r="E12" s="0">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F12" s="0">
-        <v>795961</v>
+        <v>30320</v>
       </c>
       <c r="G12" s="0">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="H12" s="0">
-        <v>0</v>
+        <v>8.6699999999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>84.209999999999994</v>
+        <v>79.340000000000003</v>
       </c>
       <c r="J12" s="0">
-        <v>1599</v>
+        <v>1223</v>
       </c>
       <c r="K12" s="0">
-        <v>5374.8699999999999</v>
+        <v>3765.3699999999999</v>
       </c>
       <c r="L12" s="0">
-        <v>27.870000000000001</v>
+        <v>21.050000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.052999999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -678,19 +681,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>924456688</v>
+        <v>213040596842</v>
       </c>
       <c r="C13" s="0">
-        <v>1115505600</v>
+        <v>252985679341</v>
       </c>
       <c r="D13" s="0">
         <v>0</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="F13" s="0">
-        <v>57913</v>
+        <v>795961</v>
       </c>
       <c r="G13" s="0">
         <v>0</v>
@@ -699,19 +702,19 @@
         <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>82.870000000000005</v>
+        <v>84.209999999999994</v>
       </c>
       <c r="J13" s="0">
-        <v>385</v>
+        <v>1599</v>
       </c>
       <c r="K13" s="0">
-        <v>0</v>
+        <v>5374.8699999999999</v>
       </c>
       <c r="L13" s="0">
-        <v>0</v>
+        <v>27.870000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="14">
@@ -719,40 +722,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>7332664097</v>
+        <v>924456688</v>
       </c>
       <c r="C14" s="0">
-        <v>9072388648</v>
+        <v>1115505600</v>
       </c>
       <c r="D14" s="0">
-        <v>160346</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F14" s="0">
-        <v>272740</v>
+        <v>57913</v>
       </c>
       <c r="G14" s="0">
-        <v>4.8200000000000003</v>
+        <v>0</v>
       </c>
       <c r="H14" s="0">
-        <v>8.1899999999999995</v>
+        <v>0</v>
       </c>
       <c r="I14" s="0">
-        <v>80.819999999999993</v>
+        <v>82.870000000000005</v>
       </c>
       <c r="J14" s="0">
-        <v>469</v>
+        <v>385</v>
       </c>
       <c r="K14" s="0">
-        <v>1162.72</v>
+        <v>0</v>
       </c>
       <c r="L14" s="0">
-        <v>16.629999999999999</v>
+        <v>0</v>
       </c>
       <c r="M14" s="0">
-        <v>0.058999999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -760,40 +763,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>6237554885</v>
+        <v>7332664097</v>
       </c>
       <c r="C15" s="0">
-        <v>7900825477</v>
+        <v>9072388648</v>
       </c>
       <c r="D15" s="0">
-        <v>55020</v>
+        <v>160346</v>
       </c>
       <c r="E15" s="0">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F15" s="0">
-        <v>237676</v>
+        <v>272740</v>
       </c>
       <c r="G15" s="0">
-        <v>1.6599999999999999</v>
+        <v>4.8200000000000003</v>
       </c>
       <c r="H15" s="0">
-        <v>2.9199999999999999</v>
+        <v>8.1899999999999995</v>
       </c>
       <c r="I15" s="0">
-        <v>78.950000000000003</v>
+        <v>80.819999999999993</v>
       </c>
       <c r="J15" s="0">
-        <v>507</v>
+        <v>469</v>
       </c>
       <c r="K15" s="0">
-        <v>1292.49</v>
+        <v>1162.72</v>
       </c>
       <c r="L15" s="0">
-        <v>20.109999999999999</v>
+        <v>16.629999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.058999999999999997</v>
       </c>
     </row>
     <row r="16">
@@ -801,40 +804,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>2361457510</v>
+        <v>7526753902</v>
       </c>
       <c r="C16" s="0">
-        <v>2894390204</v>
+        <v>9581711076</v>
       </c>
       <c r="D16" s="0">
-        <v>146181</v>
+        <v>48405</v>
       </c>
       <c r="E16" s="0">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F16" s="0">
-        <v>82369</v>
+        <v>342046</v>
       </c>
       <c r="G16" s="0">
-        <v>4.1600000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="H16" s="0">
-        <v>7.2400000000000002</v>
+        <v>2.9100000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>81.590000000000003</v>
+        <v>78.549999999999997</v>
       </c>
       <c r="J16" s="0">
-        <v>501</v>
+        <v>464</v>
       </c>
       <c r="K16" s="0">
-        <v>1222.2</v>
+        <v>1292.45</v>
       </c>
       <c r="L16" s="0">
-        <v>17.449999999999999</v>
+        <v>22.02</v>
       </c>
       <c r="M16" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="17">
@@ -842,40 +845,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>2046791540</v>
+        <v>2361457510</v>
       </c>
       <c r="C17" s="0">
-        <v>2492594724</v>
+        <v>2894390204</v>
       </c>
       <c r="D17" s="0">
-        <v>245576</v>
+        <v>146181</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F17" s="0">
-        <v>51325</v>
+        <v>82369</v>
       </c>
       <c r="G17" s="0">
-        <v>5.0599999999999996</v>
+        <v>4.1600000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>9.9399999999999995</v>
+        <v>7.2400000000000002</v>
       </c>
       <c r="I17" s="0">
-        <v>82.109999999999999</v>
+        <v>81.590000000000003</v>
       </c>
       <c r="J17" s="0">
-        <v>639</v>
+        <v>501</v>
       </c>
       <c r="K17" s="0">
-        <v>710.65999999999997</v>
+        <v>1222.2</v>
       </c>
       <c r="L17" s="0">
-        <v>9.3499999999999996</v>
+        <v>17.449999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.029000000000000001</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -883,40 +886,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>8861995601</v>
+        <v>3217095154</v>
       </c>
       <c r="C18" s="0">
-        <v>10905561178</v>
+        <v>3986361424</v>
       </c>
       <c r="D18" s="0">
-        <v>235034</v>
+        <v>175533</v>
       </c>
       <c r="E18" s="0">
         <v>76</v>
       </c>
       <c r="F18" s="0">
-        <v>248076</v>
+        <v>131319</v>
       </c>
       <c r="G18" s="0">
-        <v>5.3499999999999996</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="H18" s="0">
-        <v>9.8399999999999999</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="I18" s="0">
-        <v>81.260000000000005</v>
+        <v>80.700000000000003</v>
       </c>
       <c r="J18" s="0">
-        <v>578</v>
+        <v>399</v>
       </c>
       <c r="K18" s="0">
-        <v>966.05999999999995</v>
+        <v>1319.98</v>
       </c>
       <c r="L18" s="0">
-        <v>12.710000000000001</v>
+        <v>17.370000000000001</v>
       </c>
       <c r="M18" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -924,40 +927,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>1420097670</v>
+        <v>8861995601</v>
       </c>
       <c r="C19" s="0">
-        <v>1753881100</v>
+        <v>10905561178</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>235034</v>
       </c>
       <c r="E19" s="0">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>125604</v>
+        <v>248076</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>5.3499999999999996</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>9.8399999999999999</v>
       </c>
       <c r="I19" s="0">
-        <v>80.969999999999999</v>
+        <v>81.260000000000005</v>
       </c>
       <c r="J19" s="0">
-        <v>279</v>
+        <v>578</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>966.05999999999995</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>12.710000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0</v>
+        <v>0.040000000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -965,40 +968,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>6081711424</v>
+        <v>1420097670</v>
       </c>
       <c r="C20" s="0">
-        <v>7713542482</v>
+        <v>1753881100</v>
       </c>
       <c r="D20" s="0">
-        <v>151157</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="F20" s="0">
-        <v>288027</v>
+        <v>125604</v>
       </c>
       <c r="G20" s="0">
-        <v>5.6399999999999997</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>8.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>78.840000000000003</v>
+        <v>80.969999999999999</v>
       </c>
       <c r="J20" s="0">
-        <v>399</v>
+        <v>279</v>
       </c>
       <c r="K20" s="0">
-        <v>1428.8399999999999</v>
+        <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>21.32</v>
+        <v>0</v>
       </c>
       <c r="M20" s="0">
-        <v>0.083000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1006,40 +1009,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>11382190579</v>
+        <v>6081711424</v>
       </c>
       <c r="C21" s="0">
-        <v>14758502737</v>
+        <v>7713542482</v>
       </c>
       <c r="D21" s="0">
-        <v>211834</v>
+        <v>151157</v>
       </c>
       <c r="E21" s="0">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F21" s="0">
-        <v>336899</v>
+        <v>288027</v>
       </c>
       <c r="G21" s="0">
-        <v>4.8399999999999999</v>
+        <v>5.6399999999999997</v>
       </c>
       <c r="H21" s="0">
-        <v>9.6799999999999997</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I21" s="0">
-        <v>77.120000000000005</v>
+        <v>78.840000000000003</v>
       </c>
       <c r="J21" s="0">
-        <v>591</v>
+        <v>399</v>
       </c>
       <c r="K21" s="0">
-        <v>1420.03</v>
+        <v>1428.8399999999999</v>
       </c>
       <c r="L21" s="0">
-        <v>19.170000000000002</v>
+        <v>21.32</v>
       </c>
       <c r="M21" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="22">
@@ -1047,40 +1050,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>22627522210</v>
+        <v>11382190579</v>
       </c>
       <c r="C22" s="0">
-        <v>28022096482</v>
+        <v>14758502737</v>
       </c>
       <c r="D22" s="0">
-        <v>192037</v>
+        <v>211834</v>
       </c>
       <c r="E22" s="0">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F22" s="0">
-        <v>851153</v>
+        <v>336899</v>
       </c>
       <c r="G22" s="0">
-        <v>5.8300000000000001</v>
+        <v>4.8399999999999999</v>
       </c>
       <c r="H22" s="0">
-        <v>10.15</v>
+        <v>9.6799999999999997</v>
       </c>
       <c r="I22" s="0">
-        <v>80.75</v>
+        <v>77.120000000000005</v>
       </c>
       <c r="J22" s="0">
-        <v>500</v>
+        <v>591</v>
       </c>
       <c r="K22" s="0">
-        <v>1408.8</v>
+        <v>1420.03</v>
       </c>
       <c r="L22" s="0">
-        <v>21.77</v>
+        <v>19.170000000000002</v>
       </c>
       <c r="M22" s="0">
-        <v>0.073999999999999996</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="23">
@@ -1088,40 +1091,81 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>1029487377138</v>
+        <v>22627522210</v>
       </c>
       <c r="C23" s="0">
-        <v>1215788509319</v>
+        <v>28022096482</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>192037</v>
       </c>
       <c r="E23" s="0">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="F23" s="0">
-        <v>7998601</v>
+        <v>851153</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>5.8300000000000001</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>10.15</v>
       </c>
       <c r="I23" s="0">
-        <v>84.680000000000007</v>
+        <v>80.75</v>
       </c>
       <c r="J23" s="0">
-        <v>936</v>
+        <v>500</v>
       </c>
       <c r="K23" s="0">
-        <v>3960.2600000000002</v>
+        <v>1408.8</v>
       </c>
       <c r="L23" s="0">
-        <v>25.91</v>
+        <v>21.77</v>
       </c>
       <c r="M23" s="0">
-        <v>0.066000000000000003</v>
+        <v>0.073999999999999996</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>1046062680824</v>
+      </c>
+      <c r="C24" s="0">
+        <v>1235537403983</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0">
+        <v>131</v>
+      </c>
+      <c r="F24" s="0">
+        <v>8398644</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0">
+        <v>84.659999999999997</v>
+      </c>
+      <c r="J24" s="0">
+        <v>911</v>
+      </c>
+      <c r="K24" s="0">
+        <v>3935.23</v>
+      </c>
+      <c r="L24" s="0">
+        <v>25.949999999999999</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.067000000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Airline_Cumulative_Statistics_2019.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2019/Airline_Cumulative_Statistics_2019.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -166,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -687,7 +699,7 @@
         <v>252985679341</v>
       </c>
       <c r="D13" s="0">
-        <v>0</v>
+        <v>899057</v>
       </c>
       <c r="E13" s="0">
         <v>174</v>
@@ -696,10 +708,10 @@
         <v>795961</v>
       </c>
       <c r="G13" s="0">
-        <v>0</v>
+        <v>2.8300000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>0</v>
+        <v>10.789999999999999</v>
       </c>
       <c r="I13" s="0">
         <v>84.209999999999994</v>
@@ -1132,39 +1144,203 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
+        <v>643056477120</v>
+      </c>
+      <c r="C24" s="0">
+        <v>751898800983</v>
+      </c>
+      <c r="D24" s="0">
+        <v>822989</v>
+      </c>
+      <c r="E24" s="0">
+        <v>168</v>
+      </c>
+      <c r="F24" s="0">
+        <v>3058828</v>
+      </c>
+      <c r="G24" s="0">
+        <v>3.3500000000000001</v>
+      </c>
+      <c r="H24" s="0">
+        <v>10.77</v>
+      </c>
+      <c r="I24" s="0">
+        <v>85.519999999999996</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1286</v>
+      </c>
+      <c r="K24" s="0">
+        <v>5245.5299999999997</v>
+      </c>
+      <c r="L24" s="0">
+        <v>28.350000000000001</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.069000000000000006</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>253217876234</v>
+      </c>
+      <c r="C25" s="0">
+        <v>301395597487</v>
+      </c>
+      <c r="D25" s="0">
+        <v>636191</v>
+      </c>
+      <c r="E25" s="0">
+        <v>151</v>
+      </c>
+      <c r="F25" s="0">
+        <v>2103071</v>
+      </c>
+      <c r="G25" s="0">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="H25" s="0">
+        <v>10.59</v>
+      </c>
+      <c r="I25" s="0">
+        <v>84.019999999999996</v>
+      </c>
+      <c r="J25" s="0">
+        <v>900</v>
+      </c>
+      <c r="K25" s="0">
+        <v>3962.6500000000001</v>
+      </c>
+      <c r="L25" s="0">
+        <v>25.219999999999999</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.066000000000000003</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>78052382635</v>
+      </c>
+      <c r="C26" s="0">
+        <v>92439064582</v>
+      </c>
+      <c r="D26" s="0">
+        <v>739572</v>
+      </c>
+      <c r="E26" s="0">
+        <v>183</v>
+      </c>
+      <c r="F26" s="0">
+        <v>500599</v>
+      </c>
+      <c r="G26" s="0">
+        <v>4.0099999999999998</v>
+      </c>
+      <c r="H26" s="0">
+        <v>10.619999999999999</v>
+      </c>
+      <c r="I26" s="0">
+        <v>84.439999999999998</v>
+      </c>
+      <c r="J26" s="0">
+        <v>1004</v>
+      </c>
+      <c r="K26" s="0">
+        <v>3675.9299999999998</v>
+      </c>
+      <c r="L26" s="0">
+        <v>19.98</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.052999999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>71735944835</v>
+      </c>
+      <c r="C27" s="0">
+        <v>89803940931</v>
+      </c>
+      <c r="D27" s="0">
+        <v>147205</v>
+      </c>
+      <c r="E27" s="0">
+        <v>66</v>
+      </c>
+      <c r="F27" s="0">
+        <v>2736146</v>
+      </c>
+      <c r="G27" s="0">
+        <v>4.4900000000000002</v>
+      </c>
+      <c r="H27" s="0">
+        <v>7.7199999999999998</v>
+      </c>
+      <c r="I27" s="0">
+        <v>79.879999999999995</v>
+      </c>
+      <c r="J27" s="0">
+        <v>483</v>
+      </c>
+      <c r="K27" s="0">
+        <v>1241.3299999999999</v>
+      </c>
+      <c r="L27" s="0">
+        <v>18.550000000000001</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
         <v>1046062680824</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C28" s="0">
         <v>1235537403983</v>
       </c>
-      <c r="D24" s="0">
-        <v>0</v>
-      </c>
-      <c r="E24" s="0">
+      <c r="D28" s="0">
+        <v>582136</v>
+      </c>
+      <c r="E28" s="0">
         <v>131</v>
       </c>
-      <c r="F24" s="0">
+      <c r="F28" s="0">
         <v>8398644</v>
       </c>
-      <c r="G24" s="0">
-        <v>0</v>
-      </c>
-      <c r="H24" s="0">
-        <v>0</v>
-      </c>
-      <c r="I24" s="0">
+      <c r="G28" s="0">
+        <v>3.96</v>
+      </c>
+      <c r="H28" s="0">
+        <v>9.8399999999999999</v>
+      </c>
+      <c r="I28" s="0">
         <v>84.659999999999997</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J28" s="0">
         <v>911</v>
       </c>
-      <c r="K24" s="0">
+      <c r="K28" s="0">
         <v>3935.23</v>
       </c>
-      <c r="L24" s="0">
+      <c r="L28" s="0">
         <v>25.949999999999999</v>
       </c>
-      <c r="M24" s="0">
+      <c r="M28" s="0">
         <v>0.067000000000000004</v>
       </c>
     </row>
